--- a/jpcore-r4/feature/swg2_servicerequest/CodeSystem-jp-condition-disease-outcome-hl70241-cs.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/CodeSystem-jp-condition-disease-outcome-hl70241-cs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>copyright HL7 Japan (出典：HL7-0241)</t>
+    <t>Copyright HL7 Japan (出典：HL7-0241)</t>
   </si>
   <si>
     <t>Case Sensitive</t>
